--- a/Design/Data_Templates/SEMS_Data_Dictionary_Import_Mapping.xlsx
+++ b/Design/Data_Templates/SEMS_Data_Dictionary_Import_Mapping.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="1" r:id="R58c8717c0c6d40e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_ENTITY_MODEL" sheetId="2" r:id="R9f79e2d89c1f4e37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_DATA_DICTIONARY" sheetId="3" r:id="Ra036ffbdb0fb4690"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_IMPORT_MAPPING" sheetId="4" r:id="R2698f3e41f4f4059"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_VALIDATION_RULES" sheetId="5" r:id="Rb3846a3d320d4006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_REFERENCE_VALUES" sheetId="6" r:id="R490cedbf36294d25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_OPEN_DECISIONS" sheetId="7" r:id="R002a69092bda4412"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="1" r:id="Rac5b88aee97b4c08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_ENTITY_MODEL" sheetId="2" r:id="R0a69139660fc4035"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_DATA_DICTIONARY" sheetId="3" r:id="R134921f7f7db4aae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_IMPORT_MAPPING" sheetId="4" r:id="R44fdec9249964735"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_VALIDATION_RULES" sheetId="5" r:id="R7f53b26f87304c97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_REFERENCE_VALUES" sheetId="6" r:id="R91a466c2e6b44fd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_OPEN_DECISIONS" sheetId="7" r:id="R2ba7a6de25694088"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -63,114 +63,24 @@
   <x:borders count="20">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -326,7 +236,7 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -336,7 +246,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -388,9 +298,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -548,7 +458,7 @@
         <x:v>Key Business Rule</x:v>
       </x:c>
       <x:c r="B8" s="17" t="str">
-        <x:v>ผู้สมัครในรอบทุนใช้ round_id + student_id เป็น Business Key (รอยืนยันกรณีหลายประเภททุน)</x:v>
+        <x:v>round_id + scholarship_type_id + student_id</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -580,7 +490,7 @@
         <x:v>Identifier Rule</x:v>
       </x:c>
       <x:c r="B12" s="17" t="str">
-        <x:v>รหัสนักศึกษา โทรศัพท์ และเลขบัตรต้องอ่านเป็น Text และห้าม Scientific Notation</x:v>
+        <x:v>Student ID and phone are Text; national ID is excluded from Release 1</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -588,7 +498,7 @@
         <x:v>Next Review</x:v>
       </x:c>
       <x:c r="B13" s="17" t="str">
-        <x:v>ยืนยัน Open Decisions ใน Sheet 06 ก่อนล็อก Baseline v1.0</x:v>
+        <x:v>Confirmed responses synchronized; formal approval and measured thresholds remain pending</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -696,7 +606,7 @@
         <x:v>รหัสนักศึกษาเป็น Business Identifier</x:v>
       </x:c>
       <x:c r="F4" s="37" t="str">
-        <x:v>UUID เป็น Primary Key; ไม่ใช้เลขบัตรประชาชนเป็น Primary Identifier</x:v>
+        <x:v>UUID PK; national ID excluded from Release 1</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -713,10 +623,10 @@
         <x:v>N:1</x:v>
       </x:c>
       <x:c r="E5" s="36" t="str">
-        <x:v>Unique: round_id + applicant_id</x:v>
+        <x:v>Unique: round_id + scholarship_type_id + student_id</x:v>
       </x:c>
       <x:c r="F5" s="37" t="str">
-        <x:v>เก็บ Snapshot คณะ สาขา ชั้นปี GPA และข้อมูลประกอบการพิจารณา</x:v>
+        <x:v>Supports multiple scholarship types in one round</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1818,43 +1728,43 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="35" t="str">
-        <x:v>applicants</x:v>
+        <x:v>historical</x:v>
       </x:c>
       <x:c r="B26" s="36" t="str">
-        <x:v>citizen_id_encrypted</x:v>
+        <x:v>citizen_id_proposal</x:v>
       </x:c>
       <x:c r="C26" s="36" t="str">
-        <x:v>เลขบัตรประชาชน</x:v>
+        <x:v>Historical national-ID proposal</x:v>
       </x:c>
       <x:c r="D26" s="36" t="str">
-        <x:v>ข้อมูลจำกัดสิทธิ์ หากได้รับอนุมัติให้จัดเก็บ</x:v>
+        <x:v>Out of Scope for Release 1; requires separate lawful-need and security approval</x:v>
       </x:c>
       <x:c r="E26" s="36" t="str">
-        <x:v>TEXT</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="F26" s="36" t="str">
-        <x:v>Not in default import</x:v>
+        <x:v>Out of scope</x:v>
       </x:c>
       <x:c r="G26" s="36" t="str">
-        <x:v>Yes</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="H26" s="36" t="str">
-        <x:v>ไม่มีใน Template หลัก</x:v>
+        <x:v>No mapping</x:v>
       </x:c>
       <x:c r="I26" s="36" t="str">
-        <x:v>13 หลัก; ต้องเข้ารหัส/จำกัดสิทธิ์</x:v>
+        <x:v>Reject unsupported field</x:v>
       </x:c>
       <x:c r="J26" s="36" t="str">
-        <x:v>Restricted index only if required</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="K26" s="36" t="str">
-        <x:v>Restricted Direct Identifier</x:v>
+        <x:v>Restricted historical note</x:v>
       </x:c>
       <x:c r="L26" s="36" t="str">
-        <x:v>[Excluded by default]</x:v>
+        <x:v>Excluded</x:v>
       </x:c>
       <x:c r="M26" s="37" t="str">
-        <x:v>Open Decision; ไม่ใช้เป็น PK</x:v>
+        <x:v>Confirmed Response — Out of Scope for Release 1</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2355,7 +2265,7 @@
         <x:v>Parse decimal</x:v>
       </x:c>
       <x:c r="I39" s="36" t="str">
-        <x:v>&gt;= 0; ต้องยืนยันว่าเป็นต่อเดือน/ภาค/ปี</x:v>
+        <x:v>&gt;= 0; reporting period = SEMESTER</x:v>
       </x:c>
       <x:c r="J39" s="36" t="str">
         <x:v>-</x:v>
@@ -2367,7 +2277,7 @@
         <x:v>ค่าอุปกรณ์การศึกษา</x:v>
       </x:c>
       <x:c r="M39" s="37" t="str">
-        <x:v>Open Decision เรื่องหน่วยเวลา</x:v>
+        <x:v>Confirmed Response — per semester</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4119,7 +4029,7 @@
         <x:v>683040000-1</x:v>
       </x:c>
       <x:c r="M3" s="37" t="str">
-        <x:v>Business Key: round_id + student_id</x:v>
+        <x:v>Application key: round_id + scholarship_type_id + student_id</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4677,7 +4587,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="M17" s="37" t="str">
-        <x:v>ต้องยืนยันว่าเป็นต่อเดือน/ภาค/ปี</x:v>
+        <x:v>Unit: amount per semester</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -5504,44 +5414,44 @@
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="50" t="n">
-        <x:v>38</x:v>
+      <x:c r="A39" s="50" t="str">
+        <x:v>Historical only</x:v>
       </x:c>
       <x:c r="B39" s="36" t="str">
-        <x:v>[ไม่มีในไฟล์หลัก]</x:v>
+        <x:v>Unsupported</x:v>
       </x:c>
       <x:c r="C39" s="36" t="str">
-        <x:v>CITIZENID</x:v>
+        <x:v>[national ID field]</x:v>
       </x:c>
       <x:c r="D39" s="36" t="str">
-        <x:v>applicants</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="E39" s="36" t="str">
-        <x:v>citizen_id_encrypted</x:v>
+        <x:v>[no target field]</x:v>
       </x:c>
       <x:c r="F39" s="36" t="str">
-        <x:v>Excluded by Default</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="G39" s="36" t="str">
         <x:v>No</x:v>
       </x:c>
       <x:c r="H39" s="36" t="str">
-        <x:v>Open Decision</x:v>
+        <x:v>Out of Scope for Release 1</x:v>
       </x:c>
       <x:c r="I39" s="36" t="str">
-        <x:v>ห้ามรับเป็น Number</x:v>
+        <x:v>Reject if supplied</x:v>
       </x:c>
       <x:c r="J39" s="36" t="str">
-        <x:v>13 digits; encrypted storage</x:v>
+        <x:v>No transform</x:v>
       </x:c>
       <x:c r="K39" s="36" t="str">
-        <x:v>NULL</x:v>
+        <x:v>No persistence</x:v>
       </x:c>
       <x:c r="L39" s="36" t="str">
-        <x:v>1.4101E12 ในไฟล์เก่า</x:v>
+        <x:v>Security approval required for any future proposal</x:v>
       </x:c>
       <x:c r="M39" s="37" t="str">
-        <x:v>แนะนำแยก Restricted Import หากจำเป็น</x:v>
+        <x:v>Confirmed Response — excluded from Release 1</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -6614,7 +6524,7 @@
         <x:v>หนึ่งคนสมัครหลายประเภททุนในรอบเดียวได้หรือไม่</x:v>
       </x:c>
       <x:c r="C2" s="36" t="str">
-        <x:v>หากได้ ให้ Business Key เป็น round_id + scholarship_type_id + student_id</x:v>
+        <x:v>Confirmed: round_id + scholarship_type_id + student_id</x:v>
       </x:c>
       <x:c r="D2" s="36" t="str">
         <x:v>Unique Constraint / Import Duplicate</x:v>
@@ -6623,7 +6533,7 @@
         <x:v>งานทุน</x:v>
       </x:c>
       <x:c r="F2" s="37" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6634,7 +6544,7 @@
         <x:v>วันที่สมัครเป็นข้อมูลบังคับหรือไม่</x:v>
       </x:c>
       <x:c r="C3" s="36" t="str">
-        <x:v>Recommended; ว่างได้ตอน Import หากกระบวนการไม่ใช้</x:v>
+        <x:v>Confirmed: not a hard import requirement; validate documented formats when supplied</x:v>
       </x:c>
       <x:c r="D3" s="36" t="str">
         <x:v>Validation</x:v>
@@ -6643,7 +6553,7 @@
         <x:v>งานทุน</x:v>
       </x:c>
       <x:c r="F3" s="37" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6654,7 +6564,7 @@
         <x:v>ค่าอุปกรณ์การศึกษาเป็นต่อเดือน ต่อภาค หรือยอดรวม</x:v>
       </x:c>
       <x:c r="C4" s="36" t="str">
-        <x:v>เพิ่มหน่วยเวลาใน Template ใหม่</x:v>
+        <x:v>Confirmed: education material cost is per semester</x:v>
       </x:c>
       <x:c r="D4" s="36" t="str">
         <x:v>ชื่อ Field / รายงาน / เกณฑ์</x:v>
@@ -6663,7 +6573,7 @@
         <x:v>งานทุน</x:v>
       </x:c>
       <x:c r="F4" s="37" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6674,7 +6584,7 @@
         <x:v>ต้องจัดเก็บเลขบัตรประชาชนใน SEMS หรือไม่</x:v>
       </x:c>
       <x:c r="C5" s="36" t="str">
-        <x:v>ไม่อยู่ใน Import หลัก; หากจำเป็นให้แยก Restricted Flow และเข้ารหัส</x:v>
+        <x:v>Confirmed: Out of Scope for Release 1</x:v>
       </x:c>
       <x:c r="D5" s="36" t="str">
         <x:v>PDPA / Security / Database</x:v>
@@ -6683,7 +6593,7 @@
         <x:v>เจ้าของข้อมูล</x:v>
       </x:c>
       <x:c r="F5" s="37" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6694,7 +6604,7 @@
         <x:v>Reference Values ทางการของที่พัก สถานะครอบครัว และผู้จ่ายค่าเรียน</x:v>
       </x:c>
       <x:c r="C6" s="36" t="str">
-        <x:v>รวบรวมค่าจริงและอนุมัติ Code List</x:v>
+        <x:v>Confirmed: database-backed, versioned effective-dated code lists</x:v>
       </x:c>
       <x:c r="D6" s="36" t="str">
         <x:v>Validation / UI Filter</x:v>
@@ -6703,7 +6613,7 @@
         <x:v>งานทุน</x:v>
       </x:c>
       <x:c r="F6" s="37" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6714,7 +6624,7 @@
         <x:v>จะรองรับ Continuation Row ถึงเมื่อใด</x:v>
       </x:c>
       <x:c r="C7" s="36" t="str">
-        <x:v>Template ใหม่แยก Sheet; Legacy รองรับช่วงเปลี่ยนผ่าน</x:v>
+        <x:v>Confirmed: measure continuation-row use in UAT and first production cycle</x:v>
       </x:c>
       <x:c r="D7" s="36" t="str">
         <x:v>Importer Complexity</x:v>
@@ -6723,7 +6633,7 @@
         <x:v>งานทุน/ทีมพัฒนา</x:v>
       </x:c>
       <x:c r="F7" s="37" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6734,7 +6644,7 @@
         <x:v>Duplicate กับข้อมูลเดิมอนุญาต Update ฟิลด์ใดบ้าง</x:v>
       </x:c>
       <x:c r="C8" s="36" t="str">
-        <x:v>Default Skip; Update เฉพาะก่อนมี Evaluation</x:v>
+        <x:v>Confirmed: file duplicate Error; database duplicate Skip; never upsert</x:v>
       </x:c>
       <x:c r="D8" s="36" t="str">
         <x:v>Data Integrity / Audit</x:v>
@@ -6743,7 +6653,7 @@
         <x:v>งานทุน</x:v>
       </x:c>
       <x:c r="F8" s="37" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6754,7 +6664,7 @@
         <x:v>รูปแบบวันที่และโทรศัพท์ที่ต้องรองรับอย่างเป็นทางการ</x:v>
       </x:c>
       <x:c r="C9" s="36" t="str">
-        <x:v>Template ISO และ Text; Legacy parser เฉพาะรูปแบบประกาศ</x:v>
+        <x:v>Confirmed: ISO code where available; normalize documented legacy values</x:v>
       </x:c>
       <x:c r="D9" s="36" t="str">
         <x:v>Validation / Test Cases</x:v>
@@ -6763,7 +6673,7 @@
         <x:v>งานทุน/ทีมพัฒนา</x:v>
       </x:c>
       <x:c r="F9" s="37" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6774,7 +6684,7 @@
         <x:v>ประวัติ กยศ./ทุนเป็นข้อมูลระดับ Applicant หรือ Snapshot รายรอบ</x:v>
       </x:c>
       <x:c r="C10" s="36" t="str">
-        <x:v>เก็บระดับ Applicant พร้อม source import และแสดงในทุกรอบ</x:v>
+        <x:v>Confirmed: validation snapshot stored per application</x:v>
       </x:c>
       <x:c r="D10" s="36" t="str">
         <x:v>Data Model / Duplicate</x:v>
@@ -6783,7 +6693,7 @@
         <x:v>งานทุน</x:v>
       </x:c>
       <x:c r="F10" s="37" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6794,7 +6704,7 @@
         <x:v>Hard Required และ Required before Evaluation รายการสุดท้าย</x:v>
       </x:c>
       <x:c r="C11" s="39" t="str">
-        <x:v>ใช้รายการใน Draft นี้เป็นฐานประชุม</x:v>
+        <x:v>Confirmed: Faculty / Program / Field required before Evaluation</x:v>
       </x:c>
       <x:c r="D11" s="39" t="str">
         <x:v>Import Acceptance</x:v>
@@ -6803,7 +6713,7 @@
         <x:v>งานทุน/ผู้ประเมิน</x:v>
       </x:c>
       <x:c r="F11" s="40" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
